--- a/analysis.xlsx
+++ b/analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,17 +441,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Marks</t>
+          <t>Quiz1.pdf / 10</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Marks_1</t>
+          <t>Quiz2.pdf / 10</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Marks_2</t>
+          <t>Total Earned</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -468,257 +468,257 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2400018</t>
+          <t>271-017</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MUNEZERO CLEMENCE</t>
+          <t>NGABO KEVIN</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>35.71428571428572</v>
+        <v>50</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2400031</t>
+          <t>271-024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UMUTONIWASE Mariam</t>
+          <t>INEZA PIERRE BIENVENUE</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>51.11111111111111</v>
+        <v>75</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>240550017</t>
+          <t>271-035</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MANIRIHO MESCHACK</t>
+          <t>HIRWA AIME VALENTIN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>46.66666666666666</v>
+        <v>65</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>241-257</t>
+          <t>271-038</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aimee Sylvie Ineza</t>
+          <t>UWIMANA FABRICE</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>44.44444444444445</v>
+        <v>80</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>241-259</t>
+          <t>271-050</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IRAGIKWIYE Honorine</t>
+          <t>BARAKA Golden</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>56.34920634920635</v>
+        <v>35</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>241-261</t>
+          <t>271-059</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IRASUBIZA SAM</t>
+          <t>NISINGIZWE Evelyne</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F7" t="n">
-        <v>34.44444444444444</v>
+        <v>85</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>241-262</t>
+          <t>271-061</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IRIBAGIZA ANGELIQUE</t>
+          <t>ISHIMWE HIRWA Kelia</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>51.26984126984127</v>
+        <v>70</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>241-263</t>
+          <t>271-071</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ISHIMWE FABRICE</t>
+          <t>IGIRANEZA ERIC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>74.60317460317461</v>
+        <v>100</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>241-264</t>
+          <t>271-074</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IZABIRIZA ANGELINE</t>
+          <t>SEBUHURA Asher Jnkia</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>48.57142857142857</v>
+        <v>35</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -729,170 +729,170 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>241-268</t>
+          <t>271-079</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MUGISHA GWIZA ALAINE</t>
+          <t>KUNDWA Yasipi</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>63.96825396825398</v>
+        <v>95</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>241-271</t>
+          <t>271-102</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NDACYAYISABA PIERRE JULES</t>
+          <t>Niyogisubizo Enihakore</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
         <v>15</v>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
       <c r="F12" t="n">
-        <v>62.85714285714285</v>
+        <v>75</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>241-273</t>
+          <t>271-105</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NDIKUMANA ELISSA</t>
+          <t>Ishimwe Lucky Mike</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>58.88888888888889</v>
+        <v>75</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>241-275</t>
+          <t>271-127</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NIWEMUTONI BELYSE</t>
+          <t>Uwamahoro Mediatrice</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F14" t="n">
-        <v>64.76190476190476</v>
+        <v>80</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>241-276</t>
+          <t>271-135</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Niyigaba Nersi</t>
+          <t>IHIRWE DORCUS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>80.15873015873015</v>
+        <v>50</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>241-277</t>
+          <t>271-139</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NIYOGISUBIZO ZAMUDA</t>
+          <t>Ishimwe Olga Ivy</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>45.55555555555556</v>
+        <v>30</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>241-279</t>
+          <t>271-155</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NIYOMUKIZA PACIFIQUE</t>
+          <t>MUNYENGAGO CYUZUZO VICTOIRE</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>96.19047619047619</v>
+        <v>100</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -932,54 +932,54 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>241-280</t>
+          <t>271-174</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NIYOMWUNGERI GLORIA</t>
+          <t>Joyeuse IKIREZI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>61.11111111111111</v>
+        <v>40</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>241-284</t>
+          <t>271-217</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANO GAD</t>
+          <t>MUGISHA Ambiance</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -990,16 +990,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>241-285</t>
+          <t>271-233</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UMUGWANEZA ALICE</t>
+          <t>IYAMUBONYE Bruno</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
         <v>5</v>
@@ -1008,7 +1008,7 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>37.77777777777778</v>
+        <v>40</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1019,170 +1019,170 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>241-286</t>
+          <t>271-260</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UMUTESI Latifa</t>
+          <t>Michelle Kaliza KABANDA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>241-288</t>
+          <t>271-264</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UWASE DIVINE A</t>
+          <t>Winny UMUTESI</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>36.19047619047619</v>
+        <v>80</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>241-289</t>
+          <t>271-276</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UWIMANA GRACE</t>
+          <t>Ishallah Fredy IRASETSA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>45.55555555555556</v>
+        <v>60</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>241-290</t>
+          <t>271-308</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WIBABARA Pauline</t>
+          <t>IRASUBIZA Asgard</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F24" t="n">
-        <v>47.3015873015873</v>
+        <v>90</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>241-292</t>
+          <t>271-312</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IHIMBAZWE REPONSE</t>
+          <t>UWIRAGIYE Leah</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>69.04761904761904</v>
+        <v>50</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>241-296</t>
+          <t>271-328</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ISHIMWE Juliette</t>
+          <t>JYUYISENGA Ange</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
         <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F26" t="n">
-        <v>51.5873015873016</v>
+        <v>60</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1193,257 +1193,257 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>241-302</t>
+          <t>271-329</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MUKANDANGA JUDITH</t>
+          <t>NIYOMUKIZA Hodale</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>23.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>241-306</t>
+          <t>271-330</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NIYIGENA Henriette</t>
+          <t>ISHIMWE Janvier</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>67.30158730158729</v>
+        <v>80</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>241-307</t>
+          <t>271-345</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NIYIRORA CECILE</t>
+          <t>NSHIMIYIMANA Olivier</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F29" t="n">
-        <v>36.66666666666667</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>241-312</t>
+          <t>271-412</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NSHUTI LEON PRINCE</t>
+          <t>ISHIMWE Manzi Benique</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
         <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>37.77777777777778</v>
+        <v>50</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>241-316</t>
+          <t>271-414</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TUYISHIMIRE Jean Baptiste</t>
+          <t>UWINEZA Debora</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F31" t="n">
-        <v>47.14285714285714</v>
+        <v>65</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>241-321</t>
+          <t>271-423</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UMUTONIWASE Dalila</t>
+          <t>UWIMANA Gerardine Ciara</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
         <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F32" t="n">
-        <v>68.88888888888887</v>
+        <v>85</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>241-322</t>
+          <t>271-449</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UMWARI SYLVIE</t>
+          <t>HAKIZIMANA GASARO ANISSA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F33" t="n">
-        <v>25.55555555555555</v>
+        <v>100</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>241-323</t>
+          <t>271-455</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UTUJE ALIDIQUE</t>
+          <t>INEZA ANGE</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F34" t="n">
-        <v>42.22222222222222</v>
+        <v>90</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>241-324</t>
+          <t>271-475</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UWASE DIVINE B</t>
+          <t>GANZA RUTAGENGWA KEVIN</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>46.03174603174603</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1454,54 +1454,54 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>241-326</t>
+          <t>271-478</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>UWIMANA Solange</t>
+          <t>UMWALI KALIRE HONORINE</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36" t="n">
-        <v>59.36507936507937</v>
+        <v>35</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>241-329</t>
+          <t>271-485</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>UWIZEYE HARIMA</t>
+          <t>KARUNGI ABDRAZAK</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E37" t="n">
         <v>7</v>
       </c>
       <c r="F37" t="n">
-        <v>47.61904761904761</v>
+        <v>35</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>251-400</t>
+          <t>271-505</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GAKURU JESCA</t>
+          <t>NIYONSABA HAPPY CRIS</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>37.77777777777778</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1541,112 +1541,112 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>251-401</t>
+          <t>271-511</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ISHIMWE STEVEN</t>
+          <t>MUGISHA Romeo Cedric</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F39" t="n">
-        <v>79.2063492063492</v>
+        <v>40</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>251-402</t>
+          <t>271-513</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KANDAMA ESPERANCE</t>
+          <t>NGENDAHAYO IGIHOZO Aimee Sabrine</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
         <v>5</v>
       </c>
       <c r="F40" t="n">
-        <v>60.79365079365079</v>
+        <v>25</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>251-403</t>
+          <t>271-527</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NYAGATO SARAH</t>
+          <t>ISEZERANO UMUTONIWIMANA DEBORAH</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E41" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F41" t="n">
-        <v>34.44444444444444</v>
+        <v>90</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>251-404</t>
+          <t>271-528</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OMBENI FABRICE</t>
+          <t>KAYITESI ANNAH</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E42" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F42" t="n">
-        <v>70.95238095238095</v>
+        <v>70</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1657,85 +1657,317 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>251-405</t>
+          <t>271-529</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TURINAYO PATRICK</t>
+          <t>UWIZEYIMANA JOY</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
         <v>9</v>
       </c>
       <c r="F43" t="n">
-        <v>73.17460317460316</v>
+        <v>45</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>251-406</t>
+          <t>271-531</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>UJENEZA CHARMANTE</t>
+          <t>KARIZA HORTANCE</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F44" t="n">
-        <v>58.41269841269842</v>
+        <v>45</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Weak</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>260550015</t>
+          <t>271-532</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MAWAZO EDITH</t>
+          <t>NYAMPINGA SELENITE</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G45" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>271-533</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>IRASUBIZA BONHEUR</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="n">
+        <v>18</v>
+      </c>
+      <c r="F46" t="n">
+        <v>90</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>271-534</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>INEZA NGOGA PREATTY</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>25</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>271-535</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BAGUMA JOSEPH</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16</v>
+      </c>
+      <c r="F48" t="n">
+        <v>80</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>271-537</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>KWIZERA BIENVENU ARCHADE</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16</v>
+      </c>
+      <c r="F49" t="n">
+        <v>80</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>271-539</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MANZI CHRISTIAN</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>5</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>271-540</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NIYOGISUBIZO PACIFIQUE</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>271-560</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>IGIRANEZA Samwel Benjamin</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>271-577</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MUGISHA YVES</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="n">
+        <v>5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>7</v>
+      </c>
+      <c r="F53" t="n">
+        <v>35</v>
+      </c>
+      <c r="G53" t="inlineStr">
         <is>
           <t>Weak</t>
         </is>
